--- a/Assets/Document/云熹约定项目文档/11.配音文本/许映月配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/许映月配音文本.xlsx
@@ -29,12 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>角色分析： 性格直爽、热心、行动力强的现代女性。声音清脆，语速较快，充满活力。</t>
-  </si>
-  <si>
-    <t>197字</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>278字</t>
   </si>
   <si>
     <t>台词</t>
@@ -83,6 +80,48 @@
   </si>
   <si>
     <t>语气夸张、活泼、带着一点“霸道”的亲昵。“女人”这个称呼要说得戏谑又亲密。“最精致的幕后黑手”要带着自嘲和骄傲的矛盾感，最后“太绝了”是真心实意的安利，语气上扬，充满感染力。</t>
+  </si>
+  <si>
+    <t>“还有那些所谓的‘独立女性’人设，最后还是要靠男人来证明自己。”</t>
+  </si>
+  <si>
+    <t>带着调侃和清醒的吐槽，语速稍快，语气里有一丝不屑和见多了的无奈。</t>
+  </si>
+  <si>
+    <t>“就叫‘她说’吧，简单直接。”</t>
+  </si>
+  <si>
+    <t>果断、干脆，带着一拍即定的爽快感。像是在扔笔那一刻的灵光一现，语气笃定，不拖泥带水。</t>
+  </si>
+  <si>
+    <t>“怎么这么少？”</t>
+  </si>
+  <si>
+    <t>沮丧、有点小失落，声音可以稍微低一点。带着努力后没有得到预期回报的小委屈，像在跟自己较劲。</t>
+  </si>
+  <si>
+    <t>“我们是不是成了？”</t>
+  </si>
+  <si>
+    <t>惊喜、兴奋，眼睛发亮，语气上扬，带着不敢相信的雀跃。声音里有一点颤抖，是被认可后的激动。</t>
+  </si>
+  <si>
+    <t>“因为我们是女人，因为我们有力量。”</t>
+  </si>
+  <si>
+    <t>坚定、自信，带着自豪和力量感，但不嘶吼，是一种从容的宣告。语速平稳，像是在陈述一个终于可以大声说出来的事实。</t>
+  </si>
+  <si>
+    <t>“我们以后会一直这样吗？”</t>
+  </si>
+  <si>
+    <t>轻柔、带着一丝不确定和期待，语速放慢。像是在问一个美好的未来，声音里有珍惜，也有一点点怕失去的小心翼翼。</t>
+  </si>
+  <si>
+    <t>“然后我们重出江湖，教他们做人。”</t>
+  </si>
+  <si>
+    <t>俏皮、充满活力，带着开玩笑的嚣张。语气上扬，尾音可以带一点傲娇，像是在说“我们可厉害着呢”。</t>
   </si>
 </sst>
 </file>
@@ -95,17 +134,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -270,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,12 +311,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -494,9 +520,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -507,6 +531,28 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -630,52 +676,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
@@ -690,96 +739,99 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="72.375" style="1" customWidth="1"/>
@@ -1101,76 +1153,131 @@
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25"/>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="4" ht="18.75" spans="1:2">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="18.75" spans="1:2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" ht="37.5" spans="1:2">
       <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" ht="37.5" spans="1:2">
       <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" ht="37.5" spans="1:2">
       <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" ht="37.5" spans="1:2">
       <c r="A8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" ht="37.5" spans="1:2">
       <c r="A9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="s">
+    </row>
+    <row r="10" ht="56.25" spans="1:2">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" ht="56.25" spans="1:2">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="s">
+    </row>
+    <row r="11" ht="37.5" spans="1:2">
+      <c r="A11" s="6" t="s">
         <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="37.5" spans="1:2">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="37.5" spans="1:2">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="37.5" spans="1:2">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="37.5" spans="1:2">
+      <c r="A15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" ht="37.5" spans="1:2">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" ht="38.25" spans="1:2">
+      <c r="A17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
